--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLII/LTAIPT_A63F42B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLII/LTAIPT_A63F42B.xlsx
@@ -1,26 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c8ec10a61716621/Documentos/CUARTO PAG WEB/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_B2B22D53103F5C1CFCFF11FCD2B8F1F5F1449A99" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{42B1B4B2-D6E7-4E3E-9761-F855E1704384}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
     <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
+    <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_14">Hidden_1!$A$1:$A$4</definedName>
-    <definedName name="Hidden_210">Hidden_2!$A$1:$A$6</definedName>
+    <definedName name="Hidden_29">Hidden_2!$A$1:$A$2</definedName>
+    <definedName name="Hidden_311">Hidden_3!$A$1:$A$6</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="64">
   <si>
     <t>49013</t>
   </si>
@@ -85,6 +93,9 @@
     <t>437020</t>
   </si>
   <si>
+    <t>571945</t>
+  </si>
+  <si>
     <t>437024</t>
   </si>
   <si>
@@ -130,6 +141,9 @@
     <t>Segundo apellido</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Monto de la porción de su pensión que recibe directamente del Estado Mexicano</t>
   </si>
   <si>
@@ -148,16 +162,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>19A53F24D72B53F1EC704C1499BD3C32</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
@@ -166,10 +171,19 @@
     <t>Departamento de Recursos Humanos</t>
   </si>
   <si>
-    <t>13/01/2023</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de octubre de 2022 al 31 de diciembre de 2022, el listado de jubilados y pensionados es generado y publicado por el Instituto de Seguridad Social al Servicio de los Trabajadores del Estado como parte de las prestaciones de Ley que derivan del esquema de seguridad social prevista en la Ley del Instituto de Seguridad Social al Servicio de los Trabajadores del Estado, toda vez que el Colegio de Bachilleres del Estado de Tlaxcala no tiene un esquema propio de jubilaciones y pensiones.</t>
+    <t>7A47560C43B1F832E793E2264379DDBF</t>
+  </si>
+  <si>
+    <t>01/10/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>12/01/2024</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de octubre de 2023 al 31 de diciembre de 2023, el listado de jubilados y pensionados es generado y publicado por el Instituto de Seguridad Social al Servicio de los Trabajadores del Estado como parte de las prestaciones de Ley que derivan del esquema de seguridad social prevista en la Ley del Instituto de Seguridad Social al Servicio de los Trabajadores del Estado, toda vez que el Colegio de Bachilleres del Estado de Tlaxcala no tiene un esquema propio de jubilaciones y pensiones.</t>
   </si>
   <si>
     <t>Jubilado(a)</t>
@@ -182,6 +196,12 @@
   </si>
   <si>
     <t>Otro</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
   <si>
     <t>Quincenal</t>
@@ -205,7 +225,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -301,6 +321,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -316,44 +339,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -381,14 +404,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -416,6 +456,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -427,175 +484,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -604,20 +637,21 @@
     <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="68.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="255" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="68.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -634,7 +668,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -649,7 +683,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -675,25 +709,28 @@
         <v>6</v>
       </c>
       <c r="J4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" t="s">
         <v>10</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>8</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>9</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>7</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>11</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -736,10 +773,13 @@
       <c r="O5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -755,101 +795,108 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:15" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="P6" s="4"/>
+    </row>
+    <row r="7" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="N8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A6:P6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -857,12 +904,15 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E198">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E198" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K198">
-      <formula1>Hidden_210</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J198" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>Hidden_29</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L198" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>Hidden_311</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -870,28 +920,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -900,38 +950,58 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
